--- a/data/freight/Cass Freight Index.xlsx
+++ b/data/freight/Cass Freight Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE6C20FA-0D65-F845-9784-BCE9DFDCF15B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF6C6FE-2604-E948-9BB9-4EB693D356DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{C4FC06AE-635A-2A42-9884-3F0A165EE3F6}"/>
+    <workbookView xWindow="25160" yWindow="600" windowWidth="26040" windowHeight="26400" xr2:uid="{C4FC06AE-635A-2A42-9884-3F0A165EE3F6}"/>
   </bookViews>
   <sheets>
     <sheet name="CFIYOY" sheetId="1" r:id="rId1"/>
@@ -1912,6 +1912,39 @@
                 <c:pt idx="134">
                   <c:v>-9.8199999999999996E-2</c:v>
                 </c:pt>
+                <c:pt idx="135">
+                  <c:v>-1.61E-2</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>-0.10050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>-3.2300000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1.6299999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4.1399999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5.0099999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>-5.4899999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>-3.6799999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>-7.0400000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>3.2000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>1.3899999999999999E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3642,6 +3675,39 @@
                 </c:pt>
                 <c:pt idx="134">
                   <c:v>-5.7299999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>-1.7100000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>-8.4500000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>-2.76E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>6.1899999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4.6899999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>6.2600000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>3.7600000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>2.8299999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>7.6700000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>3.8800000000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10771,6 +10837,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E137" s="3">
+        <v>-1.61E-2</v>
+      </c>
+      <c r="F137" s="3">
+        <v>-1.7100000000000001E-2</v>
+      </c>
       <c r="I137" s="6"/>
       <c r="J137" s="6"/>
       <c r="K137" s="7"/>
@@ -10789,6 +10861,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E138" s="3">
+        <v>-0.10050000000000001</v>
+      </c>
+      <c r="F138" s="3">
+        <v>-8.4500000000000006E-2</v>
+      </c>
       <c r="I138" s="6"/>
       <c r="J138" s="6"/>
       <c r="K138" s="7"/>
@@ -10807,6 +10885,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E139" s="3">
+        <v>-3.2300000000000002E-2</v>
+      </c>
+      <c r="F139" s="3">
+        <v>-2.76E-2</v>
+      </c>
       <c r="I139" s="6"/>
       <c r="J139" s="6"/>
       <c r="K139" s="7"/>
@@ -10825,6 +10909,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E140" s="3">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="F140" s="3">
+        <v>6.1899999999999997E-2</v>
+      </c>
       <c r="I140" s="6"/>
       <c r="J140" s="6"/>
       <c r="K140" s="7"/>
@@ -10843,6 +10933,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E141" s="3">
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="F141" s="3">
+        <v>4.6899999999999997E-2</v>
+      </c>
       <c r="I141" s="6"/>
       <c r="J141" s="6"/>
       <c r="K141" s="7"/>
@@ -10861,6 +10957,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E142" s="3">
+        <v>5.0099999999999999E-2</v>
+      </c>
+      <c r="F142" s="3">
+        <v>6.2600000000000003E-2</v>
+      </c>
       <c r="I142" s="6"/>
       <c r="J142" s="6"/>
       <c r="K142" s="7"/>
@@ -10879,6 +10981,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E143" s="3">
+        <v>-5.4899999999999997E-2</v>
+      </c>
+      <c r="F143" s="3">
+        <v>3.7600000000000001E-2</v>
+      </c>
       <c r="I143" s="6"/>
       <c r="J143" s="6"/>
       <c r="K143" s="7"/>
@@ -10897,6 +11005,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E144" s="3">
+        <v>-3.6799999999999999E-2</v>
+      </c>
+      <c r="F144" s="3">
+        <v>4.3999999999999997E-2</v>
+      </c>
       <c r="I144" s="6"/>
       <c r="J144" s="6"/>
       <c r="K144" s="7"/>
@@ -10915,6 +11029,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E145" s="3">
+        <v>-7.0400000000000004E-2</v>
+      </c>
+      <c r="F145" s="3">
+        <v>2.8299999999999999E-2</v>
+      </c>
       <c r="I145" s="6"/>
       <c r="J145" s="6"/>
       <c r="K145" s="7"/>
@@ -10933,6 +11053,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E146" s="3">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="F146" s="3">
+        <v>7.6700000000000004E-2</v>
+      </c>
       <c r="I146" s="6"/>
       <c r="J146" s="6"/>
       <c r="K146" s="7"/>
@@ -10950,6 +11076,12 @@
       <c r="D147" s="4" t="str">
         <f t="shared" si="2"/>
         <v>UTC-5</v>
+      </c>
+      <c r="E147" s="3">
+        <v>1.3899999999999999E-2</v>
+      </c>
+      <c r="F147" s="3">
+        <v>3.8800000000000001E-2</v>
       </c>
       <c r="I147" s="6"/>
       <c r="J147" s="6"/>

--- a/data/freight/Cass Freight Index.xlsx
+++ b/data/freight/Cass Freight Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/freight/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF6C6FE-2604-E948-9BB9-4EB693D356DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19651F83-8E2C-6F4D-9D1A-46681ED224BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25160" yWindow="600" windowWidth="26040" windowHeight="26400" xr2:uid="{C4FC06AE-635A-2A42-9884-3F0A165EE3F6}"/>
   </bookViews>
@@ -1945,6 +1945,126 @@
                 <c:pt idx="145">
                   <c:v>1.3899999999999999E-2</c:v>
                 </c:pt>
+                <c:pt idx="146">
+                  <c:v>9.4100000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>-1.23E-2</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>2.2800000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>2.7300000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>2.7099999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>3.5299999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>8.9099999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.1368</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.1459</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.193</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.1295</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.1822</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.20630000000000001</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.2293</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.10639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.21890000000000001</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.21179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.193</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.20519999999999999</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.1973</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.20610000000000001</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.16800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.11459999999999999</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>7.5300000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2.18E-2</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>-1.2800000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5.8700000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>-3.7199999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>-2.9600000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>-3.1600000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>-4.2599999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1.95E-2</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4.6399999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>-5.0700000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>-1.77E-2</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4.8899999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>9.0200000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>9.2499999999999999E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3709,6 +3829,126 @@
                 <c:pt idx="145">
                   <c:v>3.8800000000000001E-2</c:v>
                 </c:pt>
+                <c:pt idx="146">
+                  <c:v>6.9900000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>3.8800000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>6.7500000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>8.8300000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>4.6800000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>8.2299999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>0.1038</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>7.0900000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.12230000000000001</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.1467</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>7.8700000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>0.1411</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>0.1128</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>0.13919999999999999</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>0.20580000000000001</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>0.2374</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>0.1019</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>0.17580000000000001</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>0.1825</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>0.20300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>0.17680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>0.19839999999999999</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>0.17899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>0.16289999999999999</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>0.13919999999999999</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>0.15290000000000001</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>0.1328</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>9.7799999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>0.12180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>9.74E-2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>9.6699999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>0.12690000000000001</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>0.17469999999999999</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>0.17649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>0.25469999999999998</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>0.2283</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>0.2044</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>0.19750000000000001</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>0.1923</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>0.23280000000000001</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -5035,6 +5275,24 @@
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="425"/>
+                <c:pt idx="180">
+                  <c:v>5.6500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4.99E-2</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4.9500000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5.4199999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5.7099999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4.7500000000000001E-2</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -11101,6 +11359,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E148" s="3">
+        <v>9.4100000000000003E-2</v>
+      </c>
+      <c r="F148" s="3">
+        <v>6.9900000000000004E-2</v>
+      </c>
       <c r="I148" s="6"/>
       <c r="J148" s="6"/>
       <c r="K148" s="7"/>
@@ -11119,6 +11383,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E149" s="3">
+        <v>-1.23E-2</v>
+      </c>
+      <c r="F149" s="3">
+        <v>3.8800000000000001E-2</v>
+      </c>
       <c r="I149" s="6"/>
       <c r="J149" s="6"/>
       <c r="K149" s="7"/>
@@ -11137,6 +11407,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E150" s="3">
+        <v>2.2800000000000001E-2</v>
+      </c>
+      <c r="F150" s="3">
+        <v>6.7500000000000004E-2</v>
+      </c>
       <c r="I150" s="6"/>
       <c r="J150" s="6"/>
       <c r="K150" s="7"/>
@@ -11155,6 +11431,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E151" s="3">
+        <v>2.7300000000000001E-2</v>
+      </c>
+      <c r="F151" s="3">
+        <v>8.8300000000000003E-2</v>
+      </c>
       <c r="I151" s="6"/>
       <c r="J151" s="6"/>
       <c r="K151" s="7"/>
@@ -11173,6 +11455,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E152" s="3">
+        <v>0</v>
+      </c>
+      <c r="F152" s="3">
+        <v>4.6800000000000001E-2</v>
+      </c>
       <c r="I152" s="6"/>
       <c r="J152" s="6"/>
       <c r="K152" s="7"/>
@@ -11191,6 +11479,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E153" s="3">
+        <v>2.7099999999999999E-2</v>
+      </c>
+      <c r="F153" s="3">
+        <v>8.2299999999999998E-2</v>
+      </c>
       <c r="I153" s="6"/>
       <c r="J153" s="6"/>
       <c r="K153" s="7"/>
@@ -11209,6 +11503,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E154" s="3">
+        <v>3.5299999999999998E-2</v>
+      </c>
+      <c r="F154" s="3">
+        <v>0.1038</v>
+      </c>
       <c r="I154" s="6"/>
       <c r="J154" s="6"/>
       <c r="K154" s="7"/>
@@ -11227,6 +11527,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E155" s="3">
+        <v>8.9099999999999999E-2</v>
+      </c>
+      <c r="F155" s="3">
+        <v>7.0900000000000005E-2</v>
+      </c>
       <c r="I155" s="6"/>
       <c r="J155" s="6"/>
       <c r="K155" s="7"/>
@@ -11245,6 +11551,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E156" s="3">
+        <v>0.1368</v>
+      </c>
+      <c r="F156" s="3">
+        <v>0.12230000000000001</v>
+      </c>
       <c r="I156" s="6"/>
       <c r="J156" s="6"/>
       <c r="K156" s="7"/>
@@ -11263,6 +11575,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E157" s="3">
+        <v>0.1459</v>
+      </c>
+      <c r="F157" s="3">
+        <v>0.1467</v>
+      </c>
       <c r="I157" s="6"/>
       <c r="J157" s="6"/>
       <c r="K157" s="7"/>
@@ -11281,6 +11599,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E158" s="3">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="F158" s="3">
+        <v>7.8700000000000006E-2</v>
+      </c>
       <c r="I158" s="6"/>
       <c r="J158" s="6"/>
       <c r="K158" s="7"/>
@@ -11299,6 +11623,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E159" s="3">
+        <v>0.193</v>
+      </c>
+      <c r="F159" s="3">
+        <v>0.1411</v>
+      </c>
       <c r="I159" s="6"/>
       <c r="J159" s="6"/>
       <c r="K159" s="7"/>
@@ -11317,6 +11647,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E160" s="3">
+        <v>0.1295</v>
+      </c>
+      <c r="F160" s="3">
+        <v>0.1128</v>
+      </c>
       <c r="I160" s="6"/>
       <c r="J160" s="6"/>
       <c r="K160" s="7"/>
@@ -11335,6 +11671,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E161" s="3">
+        <v>0.1822</v>
+      </c>
+      <c r="F161" s="3">
+        <v>0.13919999999999999</v>
+      </c>
       <c r="I161" s="6"/>
       <c r="J161" s="6"/>
       <c r="K161" s="7"/>
@@ -11353,6 +11695,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E162" s="3">
+        <v>0.20630000000000001</v>
+      </c>
+      <c r="F162" s="3">
+        <v>0.20580000000000001</v>
+      </c>
       <c r="I162" s="6"/>
       <c r="J162" s="6"/>
       <c r="K162" s="7"/>
@@ -11371,6 +11719,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E163" s="3">
+        <v>0.2293</v>
+      </c>
+      <c r="F163" s="3">
+        <v>0.2374</v>
+      </c>
       <c r="I163" s="6"/>
       <c r="J163" s="6"/>
       <c r="K163" s="7"/>
@@ -11389,6 +11743,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E164" s="3">
+        <v>0.10639999999999999</v>
+      </c>
+      <c r="F164" s="3">
+        <v>0.1019</v>
+      </c>
       <c r="I164" s="6"/>
       <c r="J164" s="6"/>
       <c r="K164" s="7"/>
@@ -11407,6 +11767,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E165" s="3">
+        <v>0.21890000000000001</v>
+      </c>
+      <c r="F165" s="3">
+        <v>0.17580000000000001</v>
+      </c>
       <c r="I165" s="6"/>
       <c r="J165" s="6"/>
       <c r="K165" s="7"/>
@@ -11425,6 +11791,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E166" s="3">
+        <v>0.21179999999999999</v>
+      </c>
+      <c r="F166" s="3">
+        <v>0.1825</v>
+      </c>
       <c r="I166" s="6"/>
       <c r="J166" s="6"/>
       <c r="K166" s="7"/>
@@ -11443,6 +11815,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E167" s="3">
+        <v>0.193</v>
+      </c>
+      <c r="F167" s="3">
+        <v>0.20300000000000001</v>
+      </c>
       <c r="I167" s="6"/>
       <c r="J167" s="6"/>
       <c r="K167" s="7"/>
@@ -11461,6 +11839,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E168" s="3">
+        <v>0.20519999999999999</v>
+      </c>
+      <c r="F168" s="3">
+        <v>0.17680000000000001</v>
+      </c>
       <c r="I168" s="6"/>
       <c r="J168" s="6"/>
       <c r="K168" s="7"/>
@@ -11479,6 +11863,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E169" s="3">
+        <v>0.1973</v>
+      </c>
+      <c r="F169" s="3">
+        <v>0.19839999999999999</v>
+      </c>
       <c r="I169" s="6"/>
       <c r="J169" s="6"/>
       <c r="K169" s="7"/>
@@ -11497,6 +11887,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E170" s="3">
+        <v>0.20610000000000001</v>
+      </c>
+      <c r="F170" s="3">
+        <v>0.17899999999999999</v>
+      </c>
       <c r="I170" s="6"/>
       <c r="J170" s="6"/>
       <c r="K170" s="7"/>
@@ -11515,6 +11911,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E171" s="3">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="F171" s="3">
+        <v>0.16289999999999999</v>
+      </c>
       <c r="I171" s="6"/>
       <c r="J171" s="6"/>
       <c r="K171" s="7"/>
@@ -11533,6 +11935,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E172" s="3">
+        <v>0.11459999999999999</v>
+      </c>
+      <c r="F172" s="3">
+        <v>0.13919999999999999</v>
+      </c>
       <c r="I172" s="6"/>
       <c r="J172" s="6"/>
       <c r="K172" s="7"/>
@@ -11551,6 +11959,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E173" s="3">
+        <v>7.5300000000000006E-2</v>
+      </c>
+      <c r="F173" s="3">
+        <v>0.15290000000000001</v>
+      </c>
       <c r="I173" s="6"/>
       <c r="J173" s="6"/>
       <c r="K173" s="7"/>
@@ -11569,6 +11983,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E174" s="3">
+        <v>2.18E-2</v>
+      </c>
+      <c r="F174" s="3">
+        <v>0.1328</v>
+      </c>
       <c r="I174" s="6"/>
       <c r="J174" s="6"/>
       <c r="K174" s="7"/>
@@ -11587,6 +12007,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E175" s="3">
+        <v>-1.2800000000000001E-2</v>
+      </c>
+      <c r="F175" s="3">
+        <v>9.7799999999999998E-2</v>
+      </c>
       <c r="I175" s="6"/>
       <c r="J175" s="6"/>
       <c r="K175" s="7"/>
@@ -11605,6 +12031,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E176" s="3">
+        <v>5.8700000000000002E-2</v>
+      </c>
+      <c r="F176" s="3">
+        <v>0.12180000000000001</v>
+      </c>
       <c r="I176" s="6"/>
       <c r="J176" s="6"/>
       <c r="K176" s="7"/>
@@ -11623,6 +12055,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E177" s="3">
+        <v>-3.7199999999999997E-2</v>
+      </c>
+      <c r="F177" s="3">
+        <v>9.74E-2</v>
+      </c>
       <c r="I177" s="6"/>
       <c r="J177" s="6"/>
       <c r="K177" s="7"/>
@@ -11641,6 +12079,12 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E178" s="3">
+        <v>-2.9600000000000001E-2</v>
+      </c>
+      <c r="F178" s="3">
+        <v>9.6699999999999994E-2</v>
+      </c>
       <c r="I178" s="6"/>
       <c r="J178" s="6"/>
       <c r="K178" s="7"/>
@@ -11659,6 +12103,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E179" s="3">
+        <v>-3.1600000000000003E-2</v>
+      </c>
+      <c r="F179" s="3">
+        <v>0.12690000000000001</v>
+      </c>
       <c r="I179" s="6"/>
       <c r="J179" s="6"/>
       <c r="K179" s="7"/>
@@ -11677,6 +12127,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E180" s="3">
+        <v>-4.2599999999999999E-2</v>
+      </c>
+      <c r="F180" s="3">
+        <v>0.17469999999999999</v>
+      </c>
       <c r="I180" s="6"/>
       <c r="J180" s="6"/>
       <c r="K180" s="7"/>
@@ -11695,6 +12151,12 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E181" s="3">
+        <v>1.95E-2</v>
+      </c>
+      <c r="F181" s="3">
+        <v>0.17649999999999999</v>
+      </c>
       <c r="I181" s="6"/>
       <c r="J181" s="6"/>
       <c r="K181" s="7"/>
@@ -11713,6 +12175,15 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E182" s="3">
+        <v>4.6399999999999997E-2</v>
+      </c>
+      <c r="F182" s="3">
+        <v>0.25469999999999998</v>
+      </c>
+      <c r="G182" s="3">
+        <v>5.6500000000000002E-2</v>
+      </c>
       <c r="I182" s="6"/>
       <c r="J182" s="6"/>
       <c r="K182" s="7"/>
@@ -11731,6 +12202,15 @@
         <f t="shared" si="2"/>
         <v>UTC-5</v>
       </c>
+      <c r="E183" s="3">
+        <v>-5.0700000000000002E-2</v>
+      </c>
+      <c r="F183" s="3">
+        <v>0.2283</v>
+      </c>
+      <c r="G183" s="3">
+        <v>4.99E-2</v>
+      </c>
       <c r="I183" s="6"/>
       <c r="J183" s="6"/>
       <c r="K183" s="7"/>
@@ -11749,6 +12229,15 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E184" s="3">
+        <v>-1.77E-2</v>
+      </c>
+      <c r="F184" s="3">
+        <v>0.2044</v>
+      </c>
+      <c r="G184" s="3">
+        <v>4.9500000000000002E-2</v>
+      </c>
       <c r="I184" s="6"/>
       <c r="J184" s="6"/>
       <c r="K184" s="7"/>
@@ -11767,6 +12256,15 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E185" s="3">
+        <v>4.8899999999999999E-2</v>
+      </c>
+      <c r="F185" s="3">
+        <v>0.19750000000000001</v>
+      </c>
+      <c r="G185" s="3">
+        <v>5.4199999999999998E-2</v>
+      </c>
       <c r="I185" s="6"/>
       <c r="J185" s="6"/>
       <c r="K185" s="7"/>
@@ -11785,6 +12283,15 @@
         <f t="shared" si="2"/>
         <v>UTC-4</v>
       </c>
+      <c r="E186" s="3">
+        <v>9.0200000000000002E-2</v>
+      </c>
+      <c r="F186" s="3">
+        <v>0.1923</v>
+      </c>
+      <c r="G186" s="3">
+        <v>5.7099999999999998E-2</v>
+      </c>
       <c r="I186" s="6"/>
       <c r="J186" s="6"/>
       <c r="K186" s="7"/>
@@ -11802,6 +12309,15 @@
       <c r="D187" s="4" t="str">
         <f t="shared" si="2"/>
         <v>UTC-4</v>
+      </c>
+      <c r="E187" s="3">
+        <v>9.2499999999999999E-2</v>
+      </c>
+      <c r="F187" s="3">
+        <v>0.23280000000000001</v>
+      </c>
+      <c r="G187" s="3">
+        <v>4.7500000000000001E-2</v>
       </c>
       <c r="I187" s="6"/>
       <c r="J187" s="6"/>
